--- a/themes/paymentsAndTransfers.xlsx
+++ b/themes/paymentsAndTransfers.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,279 +450,99 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Для перевода по номеру карты на главном экране выберите раздел «Платежи» -&gt; «Перевести» -&gt; «На карту» или пройдите по [ссылке]({{$temp.Card2CardLink}})</t>
+          <t xml:space="preserve">    - Ознакомиться с комиссией и лимитами на перевод можно пройдя по [ссылке](https://uralsib.ru/api/directory-engine/files/rates/tarifi-i-limiti_iafynftm.pdf)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Для перевода по номеру карты на главном экране выберите раздел «Платежи» -&gt; «Перевести» -&gt; «На карту» или пройдите по [ссылке]({{$temp.Card2CardLink}}).</t>
+          <t xml:space="preserve">    - Ознакомиться с комиссией и лимитами на перевод можно, пройдя по [ссылке](https://uralsib.ru/api/directory-engine/files/rates/tarifi-i-limiti_iafynftm.pdf)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>добавлена запятая перед деепричастием «пройдя»</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Для перевода по номеру карты на главном экране выберите раздел «Платежи» -&gt; «С карты на карту» или пройдите по [ссылке]({{$temp.Card2CardLink}})</t>
+          <t xml:space="preserve">        - Для перевода в рублях в приложении «Уралсиб Онлайн», выберите раздел «Платежи» -&gt; «По реквизитам».</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Для перевода по номеру карты на главном экране выберите раздел «Платежи» -&gt; «С карты на карту» или пройдите по [ссылке]({{$temp.Card2CardLink}}).</t>
+          <t xml:space="preserve">        - Для перевода в рублях в приложении «Уралсиб Онлайн» выберите раздел «Платежи» -&gt; «По реквизитам».</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убрана лишняя запятая — для единообразия с аналогичными фразами в файле (стр. 17, 27), где запятой нет</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Ознакомиться с комиссией и лимитами на перевод можно пройдя по [ссылке](https://uralsib.ru/api/directory-engine/files/rates/tarifi-i-limiti_iafynftm.pdf)</t>
+          <t xml:space="preserve">        - На текущий момент приостановлены внешние и исходящие платежи для клиентов - физических лиц по валютам꞉ доллар США, евро, фунт стерлингов, датская крона, японская йена, шведская крона, канадский доллар, норвежская крона, австралийский доллар, шведский франк.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Ознакомиться с комиссией и лимитами на перевод можно, пройдя по [ссылке](https://uralsib.ru/api/directory-engine/files/rates/tarifi-i-limiti_iafynftm.pdf).</t>
+          <t xml:space="preserve">        - На текущий момент приостановлены внешние и исходящие платежи для клиентов — физических лиц по валютам: доллар США, евро, фунт стерлингов, датская крона, японская йена, шведская крона, канадский доллар, норвежская крона, австралийский доллар, шведский франк.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>добавлена запятая перед деепричастием «пройдя»; добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире; нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Для перевода в рублях в приложении «Уралсиб Онлайн», выберите раздел «Платежи» -&gt; «По реквизитам».</t>
+          <t xml:space="preserve">        - Переводы в иностранной валюте за пределы банка возможны только в китайских юанях на свой счет или для оплаты страховки, услуг и обучения при предъявлении договора. Переводы возможны только на счета китайских банках, обсуживающихся на территории материкового Китая, за исключением Гонконга, Макао и Тайваня.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Для перевода в рублях в приложении «Уралсиб Онлайн» выберите раздел «Платежи» -&gt; «По реквизитам».</t>
+          <t xml:space="preserve">        - Переводы в иностранной валюте за пределы банка возможны только в китайских юанях на свой счет или для оплаты страховки, услуг и обучения при предъявлении договора. Переводы возможны только на счета китайских банков, обслуживающихся на территории материкового Китая, за исключением Гонконга, Макао и Тайваня.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>убрана лишняя запятая — для единообразия с аналогичными фразами в файле (стр. 17, 27), где запятой нет</t>
+          <t>«банках» исправлено на «банков» — согласование падежа (родительный, «счета банков»); опечатка «обсуживающихся» → «обслуживающихся»</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92</v>
+        <v>171</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Для перевода в рублях выберите раздел «Платежи» -&gt; «По реквизитам», также доступно по [ссылке]({{$temp.TransferLink}})</t>
+          <t xml:space="preserve">    - Какая информацию по переводу вас интересует?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">        - Для перевода в рублях выберите раздел «Платежи» -&gt; «По реквизитам», также доступно по [ссылке]({{$temp.TransferLink}}).</t>
+          <t xml:space="preserve">    - Какая информация по переводу вас интересует?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>94</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Для перевода в рублях выберите раздел «Платежи» -&gt; «По реквизитам», также доступно по [ссылке]({{$temp.TransferLink}})</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Для перевода в рублях выберите раздел «Платежи» -&gt; «По реквизитам», также доступно по [ссылке]({{$temp.TransferLink}}).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>98</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - На текущий момент приостановлены внешние и исходящие платежи для клиентов - физических лиц по валютам꞉ доллар США, евро, фунт стерлингов, датская крона, японская йена, шведская крона, канадский доллар, норвежская крона, австралийский доллар, шведский франк.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - На текущий момент приостановлены внешние и исходящие платежи для клиентов — физических лиц по валютам: доллар США, евро, фунт стерлингов, датская крона, японская йена, шведская крона, канадский доллар, норвежская крона, австралийский доллар, шведский франк.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире; нестандартный символ двоеточия (U+A789) заменён на обычное двоеточие</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>100</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Переводы в иностранной валюте за пределы банка возможны только в китайских юанях на свой счет или для оплаты страховки, услуг и обучения при предъявлении договора. Переводы возможны только на счета китайских банках, обсуживающихся на территории материкового Китая, за исключением Гонконга, Макао и Тайваня.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Переводы в иностранной валюте за пределы банка возможны только в китайских юанях на свой счет или для оплаты страховки, услуг и обучения при предъявлении договора. Переводы возможны только на счета китайских банков, обслуживающихся на территории материкового Китая, за исключением Гонконга, Макао и Тайваня.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>«банках» исправлено на «банков» — согласование падежа (родительный, «счета банков»); опечатка «обсуживающихся» → «обслуживающихся»</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>106</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Важно: переводы кредитных средств со счета кредитной карты не входят в льготный период</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Важно: переводы кредитных средств со счета кредитной карты не входят в льготный период.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>132</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Ознакомиться с тарифами и странами, доступными для перевода, можно по [ссылке](https://uralsib.ru/api/directory-engine/files/rates/unistrim_101023_5_mhlv9v6c.pdf)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Ознакомиться с тарифами и странами, доступными для перевода, можно по [ссылке](https://uralsib.ru/api/directory-engine/files/rates/unistrim_101023_5_mhlv9v6c.pdf).</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>138</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Телефон горячей линии Юнистрим — 8-495-744-55-55</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Телефон горячей линии Юнистрим — 8-495-744-55-55.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>166</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Ознакомиться с комиссией за перевод вы можете в разделе «Денежные переводы» по [ссылке](https://www.uralsib.ru/tarify)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Ознакомиться с комиссией за перевод вы можете в разделе «Денежные переводы» по [ссылке](https://www.uralsib.ru/tarify).</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>167</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Важно: переводы кредитных средств со счета кредитной карты не входят в льготный период</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Важно: переводы кредитных средств со счета кредитной карты не входят в льготный период.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>171</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Какая информацию по переводу вас интересует?</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Какая информация по переводу вас интересует?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>«информацию» исправлено на «информация» — согласование падежа (подлежащее должно стоять в именительном падеже)</t>
         </is>
